--- a/Bibsam_tidskriftslistor/scifree_data_portland.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_portland.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F7713C950CCDCA94F1E6E5DE6A255A7E222C7BB3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71F30DB5-1F31-451F-9D84-76CEBD1D4333}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC07ECA4-97B1-40A2-9324-0F3BA3076870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>Open</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Essays in Biochemistry</t>
   </si>
   <si>
-    <t>Emerging Topics in Life Sciences</t>
-  </si>
-  <si>
     <t>1470-8728</t>
   </si>
   <si>
@@ -116,15 +113,6 @@
   </si>
   <si>
     <t>0071-1365</t>
-  </si>
-  <si>
-    <t>https://portlandpress.com/emergtoplifesci</t>
-  </si>
-  <si>
-    <t>2397-8562</t>
-  </si>
-  <si>
-    <t>2397-8554</t>
   </si>
 </sst>
 </file>
@@ -237,10 +225,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G7" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:G7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G7">
-    <sortCondition ref="D1:D7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G6" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:G6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G6">
+    <sortCondition ref="D1:D6"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Imprint"/>
@@ -518,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -558,16 +546,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -581,16 +569,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
         <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -604,16 +592,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>0</v>
@@ -627,16 +615,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -650,44 +638,21 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -698,8 +663,8 @@
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  <conditionalFormatting sqref="E2:E6">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
